--- a/data/processed/positivacao/2023-11_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-11_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26193,7 +26193,7 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B995" t="inlineStr"/>
@@ -37441,7 +37441,7 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr"/>
@@ -66047,7 +66047,7 @@
     <row r="2529">
       <c r="A2529" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2529" t="inlineStr"/>
@@ -67744,12 +67744,12 @@
       <c r="A2595" t="inlineStr"/>
       <c r="B2595" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 7 cliente(s), não positivou 82 cliente(s) - Total vendido: R$ 5.273,86
+          <t>Vendedor 1 - VENDEDOR 01: positivou 7 cliente(s), não positivou 82 cliente(s) - Total vendido: R$ 5.273,86
 Vendedor 18 - LOJA: positivou 188 cliente(s), não positivou 708 cliente(s) - Total vendido: R$ 72.367,80
-Vendedor 3 - FERNANDA: positivou 105 cliente(s), não positivou 327 cliente(s) - Total vendido: R$ 166.090,56
-Vendedor 4 - DANIELA: positivou 83 cliente(s), não positivou 572 cliente(s) - Total vendido: R$ 55.203,44
+Vendedor 3 - VENDEDOR 03: positivou 105 cliente(s), não positivou 327 cliente(s) - Total vendido: R$ 166.090,56
+Vendedor 4 - VENDEDOR 04: positivou 83 cliente(s), não positivou 572 cliente(s) - Total vendido: R$ 55.203,44
 Vendedor 5 - SITE: positivou 5 cliente(s), não positivou 439 cliente(s) - Total vendido: R$ 1.027,67
-Vendedor 8 - RAFAEL: positivou 1 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 91,07</t>
+Vendedor 8 - VENDEDOR 08: positivou 1 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 91,07</t>
         </is>
       </c>
       <c r="C2595" t="inlineStr"/>
